--- a/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92539044597</v>
+        <v>46157.93112663472</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93112663472</v>
+        <v>46157.93367670074</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93367670074</v>
+        <v>46157.93670729067</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93670729067</v>
+        <v>46158.28193564598</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28193564598</v>
+        <v>46158.29716835074</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29716835074</v>
+        <v>46158.29789513176</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29789513176</v>
+        <v>46158.33355238301</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33355238301</v>
+        <v>46158.37210352309</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37210352309</v>
+        <v>46158.37267404106</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
